--- a/artfynd/A 42164-2024 artfynd.xlsx
+++ b/artfynd/A 42164-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123756556</v>
+        <v>123756377</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rismyrberget, Rismyrberget, Hls</t>
+          <t>Brännmyran, Brännmyran, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504134</v>
+        <v>504117</v>
       </c>
       <c r="R2" t="n">
-        <v>6847508</v>
+        <v>6847602</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,6 +760,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Två bilder tagna på samma ställe. Utföraren Kopparfors har dumpat granris inne i skyddszon på en matta av knärotsrosetter.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,12 +779,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -789,7 +794,7 @@
         <v>123756365</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -888,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123756239</v>
+        <v>123756440</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,7 +928,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -933,14 +938,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rismyrberget, Hls</t>
+          <t>Rismyrberget, Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504115</v>
+        <v>504158</v>
       </c>
       <c r="R4" t="n">
-        <v>6847499</v>
+        <v>6847511</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123756440</v>
+        <v>123756556</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,7 +1039,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1048,13 +1053,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504158</v>
+        <v>504134</v>
       </c>
       <c r="R5" t="n">
-        <v>6847511</v>
+        <v>6847508</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123756377</v>
+        <v>123756595</v>
       </c>
       <c r="B6" t="n">
-        <v>98396</v>
+        <v>79867</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,50 +1127,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Brännmyran, Brännmyran, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504117</v>
+        <v>504170</v>
       </c>
       <c r="R6" t="n">
-        <v>6847602</v>
+        <v>6847596</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,7 +1195,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Två bilder tagna på samma ställe. Utföraren Kopparfors har dumpat granris inne i skyddszon på en matta av knärotsrosetter.</t>
+          <t>Fallen sälg och döende lunglav nära avverkning.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123756595</v>
+        <v>123756239</v>
       </c>
       <c r="B7" t="n">
-        <v>79862</v>
+        <v>98502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,38 +1234,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brännmyran, Brännmyran, Hls</t>
+          <t>Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504170</v>
+        <v>504115</v>
       </c>
       <c r="R7" t="n">
-        <v>6847596</v>
+        <v>6847499</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,11 +1309,6 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Fallen sälg och döende lunglav nära avverkning.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1321,12 +1321,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 42164-2024 artfynd.xlsx
+++ b/artfynd/A 42164-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123756377</v>
+        <v>123756239</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brännmyran, Brännmyran, Hls</t>
+          <t>Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504117</v>
+        <v>504115</v>
       </c>
       <c r="R2" t="n">
-        <v>6847602</v>
+        <v>6847499</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,11 +760,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Två bilder tagna på samma ställe. Utföraren Kopparfors har dumpat granris inne i skyddszon på en matta av knärotsrosetter.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123756365</v>
+        <v>123756595</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>79869</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,41 +798,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rismyrberget, Rismyrberget, Hls</t>
+          <t>Brännmyran, Brännmyran, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504156</v>
+        <v>504170</v>
       </c>
       <c r="R3" t="n">
-        <v>6847493</v>
+        <v>6847596</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,6 +862,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fallen sälg och döende lunglav nära avverkning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,22 +881,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123756440</v>
+        <v>123756365</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,29 +926,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rismyrberget, Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504158</v>
+        <v>504156</v>
       </c>
       <c r="R4" t="n">
-        <v>6847511</v>
+        <v>6847493</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,7 +998,7 @@
         <v>123756556</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1115,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123756595</v>
+        <v>123756377</v>
       </c>
       <c r="B6" t="n">
-        <v>79867</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,41 +1118,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Brännmyran, Brännmyran, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504170</v>
+        <v>504117</v>
       </c>
       <c r="R6" t="n">
-        <v>6847596</v>
+        <v>6847602</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Fallen sälg och döende lunglav nära avverkning.</t>
+          <t>Två bilder tagna på samma ställe. Utföraren Kopparfors har dumpat granris inne i skyddszon på en matta av knärotsrosetter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123756239</v>
+        <v>123756440</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1267,14 +1267,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rismyrberget, Hls</t>
+          <t>Rismyrberget, Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504115</v>
+        <v>504158</v>
       </c>
       <c r="R7" t="n">
-        <v>6847499</v>
+        <v>6847511</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 42164-2024 artfynd.xlsx
+++ b/artfynd/A 42164-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123756239</v>
+        <v>123756595</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>79869</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rismyrberget, Hls</t>
+          <t>Brännmyran, Brännmyran, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504115</v>
+        <v>504170</v>
       </c>
       <c r="R2" t="n">
-        <v>6847499</v>
+        <v>6847596</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,6 +753,11 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fallen sälg och döende lunglav nära avverkning.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123756595</v>
+        <v>123756239</v>
       </c>
       <c r="B3" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +794,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brännmyran, Brännmyran, Hls</t>
+          <t>Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504170</v>
+        <v>504115</v>
       </c>
       <c r="R3" t="n">
-        <v>6847596</v>
+        <v>6847499</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,11 +869,6 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fallen sälg och döende lunglav nära avverkning.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -881,12 +881,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -896,7 +896,7 @@
         <v>123756365</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>123756556</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123756377</v>
+        <v>123756440</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brännmyran, Brännmyran, Hls</t>
+          <t>Rismyrberget, Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504117</v>
+        <v>504158</v>
       </c>
       <c r="R6" t="n">
-        <v>6847602</v>
+        <v>6847511</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,11 +1191,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Två bilder tagna på samma ställe. Utföraren Kopparfors har dumpat granris inne i skyddszon på en matta av knärotsrosetter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,22 +1205,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123756440</v>
+        <v>123756377</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,7 +1252,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1267,17 +1262,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rismyrberget, Rismyrberget, Hls</t>
+          <t>Brännmyran, Brännmyran, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504158</v>
+        <v>504117</v>
       </c>
       <c r="R7" t="n">
-        <v>6847511</v>
+        <v>6847602</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,6 +1302,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Två bilder tagna på samma ställe. Utföraren Kopparfors har dumpat granris inne i skyddszon på en matta av knärotsrosetter.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,15 +1321,335 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123990996</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rismyrberget, Rismyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>504092</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6847568</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mitt på hygge. Kopparfors äger marken.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123988734</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Brännmyran, Brännmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>504160</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6847496</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123988684</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Brännmyran, Brännmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>504153</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6847504</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42164-2024 artfynd.xlsx
+++ b/artfynd/A 42164-2024 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123756239</v>
+        <v>123756556</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -817,7 +817,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rismyrberget, Hls</t>
+          <t>Rismyrberget, Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504115</v>
+        <v>504134</v>
       </c>
       <c r="R3" t="n">
-        <v>6847499</v>
+        <v>6847508</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123756556</v>
+        <v>123756239</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1040,17 +1040,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rismyrberget, Rismyrberget, Hls</t>
+          <t>Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504134</v>
+        <v>504115</v>
       </c>
       <c r="R5" t="n">
-        <v>6847508</v>
+        <v>6847499</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123756440</v>
+        <v>123756377</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rismyrberget, Rismyrberget, Hls</t>
+          <t>Brännmyran, Brännmyran, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504158</v>
+        <v>504117</v>
       </c>
       <c r="R6" t="n">
-        <v>6847511</v>
+        <v>6847602</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,6 +1191,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Två bilder tagna på samma ställe. Utföraren Kopparfors har dumpat granris inne i skyddszon på en matta av knärotsrosetter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,19 +1210,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123756377</v>
+        <v>123756440</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1252,7 +1257,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1262,17 +1267,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brännmyran, Brännmyran, Hls</t>
+          <t>Rismyrberget, Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504117</v>
+        <v>504158</v>
       </c>
       <c r="R7" t="n">
-        <v>6847602</v>
+        <v>6847511</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1302,11 +1307,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Två bilder tagna på samma ställe. Utföraren Kopparfors har dumpat granris inne i skyddszon på en matta av knärotsrosetter.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,12 +1321,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 42164-2024 artfynd.xlsx
+++ b/artfynd/A 42164-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123756595</v>
+        <v>123756365</v>
       </c>
       <c r="B2" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brännmyran, Brännmyran, Hls</t>
+          <t>Rismyrberget, Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504170</v>
+        <v>504156</v>
       </c>
       <c r="R2" t="n">
-        <v>6847596</v>
+        <v>6847493</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fallen sälg och döende lunglav nära avverkning.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123756556</v>
+        <v>123756440</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -817,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -831,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504134</v>
+        <v>504158</v>
       </c>
       <c r="R3" t="n">
-        <v>6847508</v>
+        <v>6847511</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -893,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123756365</v>
+        <v>123756377</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -926,20 +921,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rismyrberget, Rismyrberget, Hls</t>
+          <t>Brännmyran, Brännmyran, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504156</v>
+        <v>504117</v>
       </c>
       <c r="R4" t="n">
-        <v>6847493</v>
+        <v>6847602</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,6 +973,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Två bilder tagna på samma ställe. Utföraren Kopparfors har dumpat granris inne i skyddszon på en matta av knärotsrosetter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,19 +992,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123756239</v>
+        <v>123756556</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1030,7 +1039,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1040,17 +1049,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rismyrberget, Hls</t>
+          <t>Rismyrberget, Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504115</v>
+        <v>504134</v>
       </c>
       <c r="R5" t="n">
-        <v>6847499</v>
+        <v>6847508</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123756377</v>
+        <v>123756595</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>79869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,50 +1127,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Brännmyran, Brännmyran, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504117</v>
+        <v>504170</v>
       </c>
       <c r="R6" t="n">
-        <v>6847602</v>
+        <v>6847596</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Två bilder tagna på samma ställe. Utföraren Kopparfors har dumpat granris inne i skyddszon på en matta av knärotsrosetter.</t>
+          <t>Fallen sälg och döende lunglav nära avverkning.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,7 +1222,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123756440</v>
+        <v>123756239</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1267,14 +1267,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rismyrberget, Rismyrberget, Hls</t>
+          <t>Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504158</v>
+        <v>504115</v>
       </c>
       <c r="R7" t="n">
-        <v>6847511</v>
+        <v>6847499</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 42164-2024 artfynd.xlsx
+++ b/artfynd/A 42164-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123756365</v>
+        <v>123756377</v>
       </c>
       <c r="B2" t="n">
         <v>98079</v>
@@ -708,20 +708,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rismyrberget, Rismyrberget, Hls</t>
+          <t>Brännmyran, Brännmyran, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504156</v>
+        <v>504117</v>
       </c>
       <c r="R2" t="n">
-        <v>6847493</v>
+        <v>6847602</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +760,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Två bilder tagna på samma ställe. Utföraren Kopparfors har dumpat granris inne i skyddszon på en matta av knärotsrosetter.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,19 +779,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123756440</v>
+        <v>123756556</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -812,7 +826,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -826,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504158</v>
+        <v>504134</v>
       </c>
       <c r="R3" t="n">
-        <v>6847511</v>
+        <v>6847508</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123756377</v>
+        <v>123756440</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -923,7 +937,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -933,17 +947,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brännmyran, Brännmyran, Hls</t>
+          <t>Rismyrberget, Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504117</v>
+        <v>504158</v>
       </c>
       <c r="R4" t="n">
-        <v>6847602</v>
+        <v>6847511</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,11 +987,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Två bilder tagna på samma ställe. Utföraren Kopparfors har dumpat granris inne i skyddszon på en matta av knärotsrosetter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,22 +1001,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123756556</v>
+        <v>123756595</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>79869</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,50 +1025,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rismyrberget, Rismyrberget, Hls</t>
+          <t>Brännmyran, Brännmyran, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504134</v>
+        <v>504170</v>
       </c>
       <c r="R5" t="n">
-        <v>6847508</v>
+        <v>6847596</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,6 +1089,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fallen sälg och döende lunglav nära avverkning.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,22 +1108,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123756595</v>
+        <v>123756239</v>
       </c>
       <c r="B6" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,38 +1132,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brännmyran, Brännmyran, Hls</t>
+          <t>Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504170</v>
+        <v>504115</v>
       </c>
       <c r="R6" t="n">
-        <v>6847596</v>
+        <v>6847499</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,11 +1207,6 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Fallen sälg och döende lunglav nära avverkning.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1210,19 +1219,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123756239</v>
+        <v>123756365</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1255,29 +1264,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rismyrberget, Hls</t>
+          <t>Rismyrberget, Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504115</v>
+        <v>504156</v>
       </c>
       <c r="R7" t="n">
-        <v>6847499</v>
+        <v>6847493</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123990996</v>
+        <v>123988734</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,50 +1345,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rismyrberget, Rismyrberget, Hls</t>
+          <t>Brännmyran, Brännmyran, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504092</v>
+        <v>504160</v>
       </c>
       <c r="R8" t="n">
-        <v>6847568</v>
+        <v>6847496</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,11 +1409,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Mitt på hygge. Kopparfors äger marken.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,19 +1423,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123988734</v>
+        <v>123988684</v>
       </c>
       <c r="B9" t="n">
         <v>78788</v>
@@ -1489,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504160</v>
+        <v>504153</v>
       </c>
       <c r="R9" t="n">
-        <v>6847496</v>
+        <v>6847504</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1551,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123988684</v>
+        <v>123990996</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,41 +1549,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Brännmyran, Brännmyran, Hls</t>
+          <t>Rismyrberget, Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504153</v>
+        <v>504092</v>
       </c>
       <c r="R10" t="n">
-        <v>6847504</v>
+        <v>6847568</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1627,6 +1622,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mitt på hygge. Kopparfors äger marken.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,12 +1641,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 42164-2024 artfynd.xlsx
+++ b/artfynd/A 42164-2024 artfynd.xlsx
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123756595</v>
+        <v>123756239</v>
       </c>
       <c r="B5" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,38 +1025,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brännmyran, Brännmyran, Hls</t>
+          <t>Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504170</v>
+        <v>504115</v>
       </c>
       <c r="R5" t="n">
-        <v>6847596</v>
+        <v>6847499</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,11 +1100,6 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fallen sälg och döende lunglav nära avverkning.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1108,22 +1112,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123756239</v>
+        <v>123756595</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>79869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,47 +1136,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rismyrberget, Hls</t>
+          <t>Brännmyran, Brännmyran, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504115</v>
+        <v>504170</v>
       </c>
       <c r="R6" t="n">
-        <v>6847499</v>
+        <v>6847596</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,6 +1202,11 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Fallen sälg och döende lunglav nära avverkning.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1219,12 +1219,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 42164-2024 artfynd.xlsx
+++ b/artfynd/A 42164-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123756377</v>
+        <v>123756365</v>
       </c>
       <c r="B2" t="n">
         <v>98079</v>
@@ -708,29 +708,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brännmyran, Brännmyran, Hls</t>
+          <t>Rismyrberget, Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504117</v>
+        <v>504156</v>
       </c>
       <c r="R2" t="n">
-        <v>6847602</v>
+        <v>6847493</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Två bilder tagna på samma ställe. Utföraren Kopparfors har dumpat granris inne i skyddszon på en matta av knärotsrosetter.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123756556</v>
+        <v>123756239</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -826,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,17 +822,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rismyrberget, Rismyrberget, Hls</t>
+          <t>Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504134</v>
+        <v>504115</v>
       </c>
       <c r="R3" t="n">
-        <v>6847508</v>
+        <v>6847499</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -902,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123756440</v>
+        <v>123756377</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -937,7 +923,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -947,17 +933,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rismyrberget, Rismyrberget, Hls</t>
+          <t>Brännmyran, Brännmyran, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504158</v>
+        <v>504117</v>
       </c>
       <c r="R4" t="n">
-        <v>6847511</v>
+        <v>6847602</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,6 +973,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Två bilder tagna på samma ställe. Utföraren Kopparfors har dumpat granris inne i skyddszon på en matta av knärotsrosetter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,19 +992,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123756239</v>
+        <v>123756440</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1048,7 +1039,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1058,14 +1049,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rismyrberget, Hls</t>
+          <t>Rismyrberget, Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504115</v>
+        <v>504158</v>
       </c>
       <c r="R5" t="n">
-        <v>6847499</v>
+        <v>6847511</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123756595</v>
+        <v>123756556</v>
       </c>
       <c r="B6" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,41 +1127,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brännmyran, Brännmyran, Hls</t>
+          <t>Rismyrberget, Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504170</v>
+        <v>504134</v>
       </c>
       <c r="R6" t="n">
-        <v>6847596</v>
+        <v>6847508</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,11 +1200,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Fallen sälg och döende lunglav nära avverkning.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,22 +1214,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123756365</v>
+        <v>123756595</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>79869</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,41 +1238,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rismyrberget, Rismyrberget, Hls</t>
+          <t>Brännmyran, Brännmyran, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504156</v>
+        <v>504170</v>
       </c>
       <c r="R7" t="n">
-        <v>6847493</v>
+        <v>6847596</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,6 +1302,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Fallen sälg och döende lunglav nära avverkning.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,22 +1321,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123988734</v>
+        <v>123990996</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,41 +1345,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brännmyran, Brännmyran, Hls</t>
+          <t>Rismyrberget, Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504160</v>
+        <v>504092</v>
       </c>
       <c r="R8" t="n">
-        <v>6847496</v>
+        <v>6847568</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1409,6 +1418,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mitt på hygge. Kopparfors äger marken.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,12 +1437,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1537,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123990996</v>
+        <v>123988734</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,50 +1563,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rismyrberget, Rismyrberget, Hls</t>
+          <t>Brännmyran, Brännmyran, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504092</v>
+        <v>504160</v>
       </c>
       <c r="R10" t="n">
-        <v>6847568</v>
+        <v>6847496</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1622,11 +1627,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mitt på hygge. Kopparfors äger marken.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,12 +1641,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 42164-2024 artfynd.xlsx
+++ b/artfynd/A 42164-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123756377</v>
+        <v>123756239</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brännmyran, Brännmyran, Hls</t>
+          <t>Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504117</v>
+        <v>504115</v>
       </c>
       <c r="R2" t="n">
-        <v>6847602</v>
+        <v>6847499</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,11 +760,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Två bilder tagna på samma ställe. Utföraren Kopparfors har dumpat granris inne i skyddszon på en matta av knärotsrosetter.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,19 +774,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123756440</v>
+        <v>123756365</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -824,29 +819,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rismyrberget, Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504158</v>
+        <v>504156</v>
       </c>
       <c r="R3" t="n">
-        <v>6847511</v>
+        <v>6847493</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -902,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123756556</v>
+        <v>123756440</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -937,7 +923,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -951,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504134</v>
+        <v>504158</v>
       </c>
       <c r="R4" t="n">
-        <v>6847508</v>
+        <v>6847511</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123756365</v>
+        <v>123756595</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,41 +1011,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rismyrberget, Rismyrberget, Hls</t>
+          <t>Brännmyran, Brännmyran, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504156</v>
+        <v>504170</v>
       </c>
       <c r="R5" t="n">
-        <v>6847493</v>
+        <v>6847596</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,6 +1075,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fallen sälg och döende lunglav nära avverkning.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,19 +1094,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123756239</v>
+        <v>123756556</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1150,7 +1141,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1160,17 +1151,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rismyrberget, Hls</t>
+          <t>Rismyrberget, Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504115</v>
+        <v>504134</v>
       </c>
       <c r="R6" t="n">
-        <v>6847499</v>
+        <v>6847508</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123756595</v>
+        <v>123756377</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,41 +1229,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Brännmyran, Brännmyran, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504170</v>
+        <v>504117</v>
       </c>
       <c r="R7" t="n">
-        <v>6847596</v>
+        <v>6847602</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Fallen sälg och döende lunglav nära avverkning.</t>
+          <t>Två bilder tagna på samma ställe. Utföraren Kopparfors har dumpat granris inne i skyddszon på en matta av knärotsrosetter.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 42164-2024 artfynd.xlsx
+++ b/artfynd/A 42164-2024 artfynd.xlsx
@@ -1333,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123990996</v>
+        <v>123988734</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,50 +1345,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rismyrberget, Rismyrberget, Hls</t>
+          <t>Brännmyran, Brännmyran, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504092</v>
+        <v>504160</v>
       </c>
       <c r="R8" t="n">
-        <v>6847568</v>
+        <v>6847496</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,11 +1409,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Mitt på hygge. Kopparfors äger marken.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,12 +1423,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1551,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123988734</v>
+        <v>123990996</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,41 +1549,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Brännmyran, Brännmyran, Hls</t>
+          <t>Rismyrberget, Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504160</v>
+        <v>504092</v>
       </c>
       <c r="R10" t="n">
-        <v>6847496</v>
+        <v>6847568</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1627,6 +1622,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mitt på hygge. Kopparfors äger marken.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,12 +1641,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 42164-2024 artfynd.xlsx
+++ b/artfynd/A 42164-2024 artfynd.xlsx
@@ -1333,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123988734</v>
+        <v>123990996</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,41 +1345,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brännmyran, Brännmyran, Hls</t>
+          <t>Rismyrberget, Rismyrberget, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504160</v>
+        <v>504092</v>
       </c>
       <c r="R8" t="n">
-        <v>6847496</v>
+        <v>6847568</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1409,6 +1418,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mitt på hygge. Kopparfors äger marken.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,12 +1437,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1537,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123990996</v>
+        <v>123988734</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,50 +1563,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rismyrberget, Rismyrberget, Hls</t>
+          <t>Brännmyran, Brännmyran, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504092</v>
+        <v>504160</v>
       </c>
       <c r="R10" t="n">
-        <v>6847568</v>
+        <v>6847496</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1622,11 +1627,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mitt på hygge. Kopparfors äger marken.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,12 +1641,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 42164-2024 artfynd.xlsx
+++ b/artfynd/A 42164-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1651,6 +1651,108 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125037539</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57624</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rismyrberget, Rismyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>503924</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6847551</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42164-2024 artfynd.xlsx
+++ b/artfynd/A 42164-2024 artfynd.xlsx
@@ -1656,7 +1656,7 @@
         <v>125037539</v>
       </c>
       <c r="B11" t="n">
-        <v>57624</v>
+        <v>57738</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
